--- a/artfynd/A 60162-2022 artfynd.xlsx
+++ b/artfynd/A 60162-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60162-2022 artfynd.xlsx
+++ b/artfynd/A 60162-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100618992</v>
+        <v>100618690</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471918.218774765</v>
+        <v>471843</v>
       </c>
       <c r="R2" t="n">
-        <v>6627848.197908147</v>
+        <v>6627794</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>dikad skog/beskogad f.d. torvtäkt</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +780,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,6 +795,967 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>108172570</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Knuthöjdsvägen, Hällefors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>471698</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6628019</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erling Lillberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erling Lillberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100620067</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sångsvägen, Hällefors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>471886</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6627783</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Samlade bomaterial och flög iväg med det.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100619097</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sångsvägen, Hällefors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>471963</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6627981</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108172567</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Knuthöjdsvägen, Hällefors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>471698</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6628019</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erling Lillberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erling Lillberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100618863</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sångsvägen, Hällefors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>471902</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6627826</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108172573</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Knuthöjdsvägen, Hällefors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>471698</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6628019</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erling Lillberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erling Lillberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108172574</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Knuthöjdsvägen, Hällefors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>471698</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6628019</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erling Lillberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erling Lillberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100618992</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sångsvägen, Hällefors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>471918</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6627848</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>dikad skog/beskogad f.d. torvtäkt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60162-2022 artfynd.xlsx
+++ b/artfynd/A 60162-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100618690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108172570</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100620067</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1159,6 +1179,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100619097</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108172567</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1401,6 +1431,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100618863</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1520,6 +1555,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108172573</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1639,6 +1679,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108172574</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1756,8 +1801,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100618992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>